--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119653895</v>
+        <v>119653870</v>
       </c>
       <c r="B2" t="n">
-        <v>57316</v>
+        <v>57463</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579810</v>
+        <v>579770</v>
       </c>
       <c r="R2" t="n">
-        <v>6398204</v>
+        <v>6398150</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -763,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Först hörd på norra sidan av gölen, men flög sedan över till den södra.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119653870</v>
+        <v>119653895</v>
       </c>
       <c r="B3" t="n">
-        <v>57463</v>
+        <v>57316</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -846,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579770</v>
+        <v>579810</v>
       </c>
       <c r="R3" t="n">
-        <v>6398150</v>
+        <v>6398204</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -882,6 +877,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Först hörd på norra sidan av gölen, men flög sedan över till den södra.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119653870</v>
+        <v>119653895</v>
       </c>
       <c r="B2" t="n">
-        <v>57463</v>
+        <v>57316</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579770</v>
+        <v>579810</v>
       </c>
       <c r="R2" t="n">
-        <v>6398150</v>
+        <v>6398204</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -763,6 +763,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Först hörd på norra sidan av gölen, men flög sedan över till den södra.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119653895</v>
+        <v>119653870</v>
       </c>
       <c r="B3" t="n">
-        <v>57316</v>
+        <v>57463</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +810,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579810</v>
+        <v>579770</v>
       </c>
       <c r="R3" t="n">
-        <v>6398204</v>
+        <v>6398150</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,11 +882,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Först hörd på norra sidan av gölen, men flög sedan över till den södra.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119653895</v>
       </c>
       <c r="B2" t="n">
-        <v>57316</v>
+        <v>57484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119653895</v>
       </c>
       <c r="B2" t="n">
-        <v>57484</v>
+        <v>57487</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119653895</v>
       </c>
       <c r="B2" t="n">
-        <v>57487</v>
+        <v>57493</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119653895</v>
       </c>
       <c r="B2" t="n">
-        <v>57493</v>
+        <v>57496</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119653895</v>
       </c>
       <c r="B2" t="n">
-        <v>57496</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 26992-2024 artfynd.xlsx
+++ b/artfynd/A 26992-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119653895</v>
+        <v>119653870</v>
       </c>
       <c r="B2" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579810</v>
+        <v>579770</v>
       </c>
       <c r="R2" t="n">
-        <v>6398204</v>
+        <v>6398150</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -763,11 +758,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-09-09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Först hörd på norra sidan av gölen, men flög sedan över till den södra.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,15 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119653870</v>
+        <v>119653895</v>
       </c>
       <c r="B3" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,21 +795,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -846,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579770</v>
+        <v>579810</v>
       </c>
       <c r="R3" t="n">
-        <v>6398150</v>
+        <v>6398204</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -882,6 +867,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Först hörd på norra sidan av gölen, men flög sedan över till den södra.</t>
         </is>
       </c>
       <c r="AD3" t="b">
